--- a/output/pdf_financials_xlsx/LFLR.xlsx
+++ b/output/pdf_financials_xlsx/LFLR.xlsx
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.005109</v>
       </c>
     </row>
     <row r="13">
@@ -867,7 +867,7 @@
         <v>-3.633666</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.248337</v>
+        <v>-3.253446</v>
       </c>
     </row>
     <row r="28">
@@ -899,7 +899,7 @@
         <v>-3.633666</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.248337</v>
+        <v>-3.253446</v>
       </c>
     </row>
     <row r="30">
@@ -5941,7 +5941,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">

--- a/output/pdf_financials_xlsx/LFLR.xlsx
+++ b/output/pdf_financials_xlsx/LFLR.xlsx
@@ -2057,13 +2057,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.017667</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>-0.048922</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.176098</v>
       </c>
     </row>
     <row r="102">
@@ -2268,7 +2268,7 @@
         <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="D114" s="3" t="n">
         <v>0</v>
@@ -4311,7 +4311,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E54" s="5" t="n">
         <v>-0.017667</v>
       </c>
@@ -4369,7 +4373,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -5187,7 +5195,11 @@
           <t>Share issued for cash</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E82" s="5" t="n">
         <v>0.01</v>
       </c>
